--- a/data/metadata_raw/consumer_goods_output.xlsx
+++ b/data/metadata_raw/consumer_goods_output.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="1231">
   <si>
     <t>Code</t>
   </si>
@@ -2846,6 +2846,9 @@
     <t>Бухоро тумани</t>
   </si>
   <si>
+    <t>Вобкент тумани</t>
+  </si>
+  <si>
     <t>Ғиждувон тумани</t>
   </si>
   <si>
@@ -3584,7 +3587,7 @@
     <t>2022-06-29</t>
   </si>
   <si>
-    <t>2022-08-16</t>
+    <t>2023-09-04</t>
   </si>
   <si>
     <t>1.02.01.0005</t>
@@ -6444,7 +6447,7 @@
         <v>722</v>
       </c>
       <c r="E43" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="F43">
         <v>19.3</v>
@@ -6500,7 +6503,7 @@
         <v>723</v>
       </c>
       <c r="E44" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="F44">
         <v>34.1</v>
@@ -6556,7 +6559,7 @@
         <v>724</v>
       </c>
       <c r="E45" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F45">
         <v>11.9</v>
@@ -6612,7 +6615,7 @@
         <v>725</v>
       </c>
       <c r="E46" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F46">
         <v>30.7</v>
@@ -6668,7 +6671,7 @@
         <v>726</v>
       </c>
       <c r="E47" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F47">
         <v>351.3</v>
@@ -6724,7 +6727,7 @@
         <v>727</v>
       </c>
       <c r="E48" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="F48">
         <v>4.7</v>
@@ -6780,7 +6783,7 @@
         <v>728</v>
       </c>
       <c r="E49" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="F49">
         <v>15</v>
@@ -6836,7 +6839,7 @@
         <v>729</v>
       </c>
       <c r="E50" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F50">
         <v>28.7</v>
@@ -6892,7 +6895,7 @@
         <v>730</v>
       </c>
       <c r="E51" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F51">
         <v>8.9</v>
@@ -6948,7 +6951,7 @@
         <v>731</v>
       </c>
       <c r="E52" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="F52">
         <v>256.9</v>
@@ -7004,7 +7007,7 @@
         <v>732</v>
       </c>
       <c r="E53" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="F53">
         <v>112.9</v>
@@ -7060,7 +7063,7 @@
         <v>733</v>
       </c>
       <c r="E54" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F54">
         <v>3.5</v>
@@ -7116,7 +7119,7 @@
         <v>734</v>
       </c>
       <c r="E55" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="F55">
         <v>23.6</v>
@@ -7172,7 +7175,7 @@
         <v>735</v>
       </c>
       <c r="E56" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F56">
         <v>14.3</v>
@@ -7228,7 +7231,7 @@
         <v>736</v>
       </c>
       <c r="E57" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F57">
         <v>18.6</v>
@@ -7284,7 +7287,7 @@
         <v>737</v>
       </c>
       <c r="E58" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F58">
         <v>42</v>
@@ -7340,7 +7343,7 @@
         <v>738</v>
       </c>
       <c r="E59" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="F59">
         <v>11.4</v>
@@ -7396,7 +7399,7 @@
         <v>739</v>
       </c>
       <c r="E60" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F60">
         <v>5</v>
@@ -7452,7 +7455,7 @@
         <v>740</v>
       </c>
       <c r="E61" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F61">
         <v>6.7</v>
@@ -7508,7 +7511,7 @@
         <v>741</v>
       </c>
       <c r="E62" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="F62">
         <v>3.6</v>
@@ -7564,7 +7567,7 @@
         <v>742</v>
       </c>
       <c r="E63" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="F63">
         <v>5.4</v>
@@ -7620,7 +7623,7 @@
         <v>743</v>
       </c>
       <c r="E64" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F64">
         <v>7.7</v>
@@ -7676,7 +7679,7 @@
         <v>744</v>
       </c>
       <c r="E65" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="F65">
         <v>2.2</v>
@@ -7732,7 +7735,7 @@
         <v>745</v>
       </c>
       <c r="E66" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="F66">
         <v>651.7</v>
@@ -7788,7 +7791,7 @@
         <v>746</v>
       </c>
       <c r="E67" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F67">
         <v>263.3</v>
@@ -7844,7 +7847,7 @@
         <v>747</v>
       </c>
       <c r="E68" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -7900,7 +7903,7 @@
         <v>748</v>
       </c>
       <c r="E69" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -7956,7 +7959,7 @@
         <v>749</v>
       </c>
       <c r="E70" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F70">
         <v>6.2</v>
@@ -8012,7 +8015,7 @@
         <v>750</v>
       </c>
       <c r="E71" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F71">
         <v>3.5</v>
@@ -8068,7 +8071,7 @@
         <v>751</v>
       </c>
       <c r="E72" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="F72">
         <v>35.7</v>
@@ -8124,7 +8127,7 @@
         <v>752</v>
       </c>
       <c r="E73" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F73">
         <v>12.9</v>
@@ -8180,7 +8183,7 @@
         <v>753</v>
       </c>
       <c r="E74" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F74">
         <v>79.59999999999999</v>
@@ -8236,7 +8239,7 @@
         <v>754</v>
       </c>
       <c r="E75" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="F75">
         <v>29.6</v>
@@ -8292,7 +8295,7 @@
         <v>755</v>
       </c>
       <c r="E76" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F76">
         <v>7.8</v>
@@ -8348,7 +8351,7 @@
         <v>756</v>
       </c>
       <c r="E77" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F77">
         <v>9.4</v>
@@ -8404,7 +8407,7 @@
         <v>757</v>
       </c>
       <c r="E78" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F78">
         <v>9.300000000000001</v>
@@ -8460,7 +8463,7 @@
         <v>758</v>
       </c>
       <c r="E79" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F79">
         <v>4.7</v>
@@ -8516,7 +8519,7 @@
         <v>759</v>
       </c>
       <c r="E80" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F80">
         <v>22.6</v>
@@ -8572,7 +8575,7 @@
         <v>760</v>
       </c>
       <c r="E81" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="F81">
         <v>141.4</v>
@@ -8628,7 +8631,7 @@
         <v>761</v>
       </c>
       <c r="E82" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F82">
         <v>25.7</v>
@@ -8684,7 +8687,7 @@
         <v>762</v>
       </c>
       <c r="E83" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F83">
         <v>455.8</v>
@@ -8740,7 +8743,7 @@
         <v>763</v>
       </c>
       <c r="E84" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F84">
         <v>312.7</v>
@@ -8796,7 +8799,7 @@
         <v>764</v>
       </c>
       <c r="E85" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F85">
         <v>40.8</v>
@@ -8852,7 +8855,7 @@
         <v>765</v>
       </c>
       <c r="E86" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -8908,7 +8911,7 @@
         <v>766</v>
       </c>
       <c r="E87" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F87">
         <v>3.4</v>
@@ -8964,7 +8967,7 @@
         <v>767</v>
       </c>
       <c r="E88" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F88">
         <v>30.4</v>
@@ -9020,7 +9023,7 @@
         <v>768</v>
       </c>
       <c r="E89" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F89">
         <v>5.4</v>
@@ -9076,7 +9079,7 @@
         <v>769</v>
       </c>
       <c r="E90" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F90">
         <v>32.3</v>
@@ -9132,7 +9135,7 @@
         <v>770</v>
       </c>
       <c r="E91" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F91">
         <v>5.8</v>
@@ -9188,7 +9191,7 @@
         <v>771</v>
       </c>
       <c r="E92" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F92">
         <v>1.3</v>
@@ -9244,7 +9247,7 @@
         <v>772</v>
       </c>
       <c r="E93" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F93">
         <v>5.2</v>
@@ -9300,7 +9303,7 @@
         <v>773</v>
       </c>
       <c r="E94" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F94">
         <v>18.4</v>
@@ -9356,7 +9359,7 @@
         <v>774</v>
       </c>
       <c r="E95" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F95">
         <v>581.8</v>
@@ -9412,7 +9415,7 @@
         <v>775</v>
       </c>
       <c r="E96" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F96">
         <v>306.8</v>
@@ -9468,7 +9471,7 @@
         <v>776</v>
       </c>
       <c r="E97" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F97">
         <v>4.1</v>
@@ -9524,7 +9527,7 @@
         <v>777</v>
       </c>
       <c r="E98" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F98">
         <v>20.1</v>
@@ -9580,7 +9583,7 @@
         <v>778</v>
       </c>
       <c r="E99" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F99">
         <v>47.8</v>
@@ -9636,7 +9639,7 @@
         <v>779</v>
       </c>
       <c r="E100" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="F100">
         <v>6.7</v>
@@ -9692,7 +9695,7 @@
         <v>780</v>
       </c>
       <c r="E101" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F101">
         <v>9.4</v>
@@ -9748,7 +9751,7 @@
         <v>781</v>
       </c>
       <c r="E102" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F102">
         <v>14.3</v>
@@ -9804,7 +9807,7 @@
         <v>782</v>
       </c>
       <c r="E103" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="F103">
         <v>20.9</v>
@@ -9860,7 +9863,7 @@
         <v>783</v>
       </c>
       <c r="E104" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F104">
         <v>91</v>
@@ -9916,7 +9919,7 @@
         <v>784</v>
       </c>
       <c r="E105" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F105">
         <v>19.8</v>
@@ -9972,7 +9975,7 @@
         <v>785</v>
       </c>
       <c r="E106" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F106">
         <v>22.3</v>
@@ -10028,7 +10031,7 @@
         <v>786</v>
       </c>
       <c r="E107" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F107">
         <v>18.4</v>
@@ -10084,7 +10087,7 @@
         <v>787</v>
       </c>
       <c r="E108" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="F108">
         <v>1412.4</v>
@@ -10140,7 +10143,7 @@
         <v>788</v>
       </c>
       <c r="E109" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F109">
         <v>938.6</v>
@@ -10196,7 +10199,7 @@
         <v>789</v>
       </c>
       <c r="E110" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="F110">
         <v>42</v>
@@ -10252,7 +10255,7 @@
         <v>790</v>
       </c>
       <c r="E111" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="F111">
         <v>10.2</v>
@@ -10308,7 +10311,7 @@
         <v>791</v>
       </c>
       <c r="E112" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F112">
         <v>10.9</v>
@@ -10364,7 +10367,7 @@
         <v>792</v>
       </c>
       <c r="E113" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F113">
         <v>67.40000000000001</v>
@@ -10420,7 +10423,7 @@
         <v>793</v>
       </c>
       <c r="E114" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="F114">
         <v>9.4</v>
@@ -10476,7 +10479,7 @@
         <v>794</v>
       </c>
       <c r="E115" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F115">
         <v>32.1</v>
@@ -10532,7 +10535,7 @@
         <v>795</v>
       </c>
       <c r="E116" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F116">
         <v>9.4</v>
@@ -10588,7 +10591,7 @@
         <v>796</v>
       </c>
       <c r="E117" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F117">
         <v>45.5</v>
@@ -10644,7 +10647,7 @@
         <v>797</v>
       </c>
       <c r="E118" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="F118">
         <v>13.3</v>
@@ -10700,7 +10703,7 @@
         <v>798</v>
       </c>
       <c r="E119" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="F119">
         <v>25</v>
@@ -10756,7 +10759,7 @@
         <v>799</v>
       </c>
       <c r="E120" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="F120">
         <v>13.6</v>
@@ -10812,7 +10815,7 @@
         <v>800</v>
       </c>
       <c r="E121" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F121">
         <v>79.2</v>
@@ -10868,7 +10871,7 @@
         <v>801</v>
       </c>
       <c r="E122" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F122">
         <v>4.8</v>
@@ -10924,7 +10927,7 @@
         <v>802</v>
       </c>
       <c r="E123" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F123">
         <v>77.7</v>
@@ -10980,7 +10983,7 @@
         <v>803</v>
       </c>
       <c r="E124" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="F124">
         <v>33.2</v>
@@ -11036,7 +11039,7 @@
         <v>804</v>
       </c>
       <c r="E125" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F125">
         <v>290.7</v>
@@ -11092,7 +11095,7 @@
         <v>805</v>
       </c>
       <c r="E126" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="F126">
         <v>32.8</v>
@@ -11148,7 +11151,7 @@
         <v>806</v>
       </c>
       <c r="E127" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="F127">
         <v>9.6</v>
@@ -11204,7 +11207,7 @@
         <v>807</v>
       </c>
       <c r="E128" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F128">
         <v>10.5</v>
@@ -11260,7 +11263,7 @@
         <v>808</v>
       </c>
       <c r="E129" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -11316,7 +11319,7 @@
         <v>809</v>
       </c>
       <c r="E130" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F130">
         <v>15.4</v>
@@ -11372,7 +11375,7 @@
         <v>810</v>
       </c>
       <c r="E131" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="F131">
         <v>14.1</v>
@@ -11428,7 +11431,7 @@
         <v>811</v>
       </c>
       <c r="E132" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F132">
         <v>52.4</v>
@@ -11484,7 +11487,7 @@
         <v>812</v>
       </c>
       <c r="E133" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F133">
         <v>12.5</v>
@@ -11540,7 +11543,7 @@
         <v>813</v>
       </c>
       <c r="E134" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="F134">
         <v>13.2</v>
@@ -11596,7 +11599,7 @@
         <v>814</v>
       </c>
       <c r="E135" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="F135">
         <v>10.4</v>
@@ -11652,7 +11655,7 @@
         <v>815</v>
       </c>
       <c r="E136" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F136">
         <v>15.9</v>
@@ -11708,7 +11711,7 @@
         <v>816</v>
       </c>
       <c r="E137" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F137">
         <v>14.1</v>
@@ -11764,7 +11767,7 @@
         <v>817</v>
       </c>
       <c r="E138" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="F138">
         <v>12.6</v>
@@ -11820,7 +11823,7 @@
         <v>818</v>
       </c>
       <c r="E139" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="F139">
         <v>21.2</v>
@@ -11876,7 +11879,7 @@
         <v>819</v>
       </c>
       <c r="E140" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F140">
         <v>55.9</v>
@@ -11932,7 +11935,7 @@
         <v>820</v>
       </c>
       <c r="E141" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="F141">
         <v>252.9</v>
@@ -11988,7 +11991,7 @@
         <v>821</v>
       </c>
       <c r="E142" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F142">
         <v>54.7</v>
@@ -12044,7 +12047,7 @@
         <v>822</v>
       </c>
       <c r="E143" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F143">
         <v>3</v>
@@ -12100,7 +12103,7 @@
         <v>823</v>
       </c>
       <c r="E144" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F144">
         <v>13.2</v>
@@ -12156,7 +12159,7 @@
         <v>824</v>
       </c>
       <c r="E145" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="F145">
         <v>11</v>
@@ -12212,7 +12215,7 @@
         <v>825</v>
       </c>
       <c r="E146" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F146">
         <v>14.7</v>
@@ -12268,7 +12271,7 @@
         <v>826</v>
       </c>
       <c r="E147" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F147">
         <v>25.1</v>
@@ -12324,7 +12327,7 @@
         <v>827</v>
       </c>
       <c r="E148" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F148">
         <v>11.1</v>
@@ -12380,7 +12383,7 @@
         <v>828</v>
       </c>
       <c r="E149" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="F149">
         <v>9.6</v>
@@ -12436,7 +12439,7 @@
         <v>829</v>
       </c>
       <c r="E150" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F150">
         <v>9.5</v>
@@ -12492,7 +12495,7 @@
         <v>830</v>
       </c>
       <c r="E151" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="F151">
         <v>83.7</v>
@@ -12548,7 +12551,7 @@
         <v>831</v>
       </c>
       <c r="E152" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F152">
         <v>17.3</v>
@@ -12604,7 +12607,7 @@
         <v>832</v>
       </c>
       <c r="E153" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F153">
         <v>1335.3</v>
@@ -12660,7 +12663,7 @@
         <v>833</v>
       </c>
       <c r="E154" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -12716,7 +12719,7 @@
         <v>834</v>
       </c>
       <c r="E155" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F155">
         <v>25.5</v>
@@ -12772,7 +12775,7 @@
         <v>835</v>
       </c>
       <c r="E156" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F156">
         <v>32.7</v>
@@ -12828,7 +12831,7 @@
         <v>836</v>
       </c>
       <c r="E157" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="F157">
         <v>130.7</v>
@@ -12884,7 +12887,7 @@
         <v>837</v>
       </c>
       <c r="E158" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="F158">
         <v>75</v>
@@ -12940,7 +12943,7 @@
         <v>838</v>
       </c>
       <c r="E159" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -12996,7 +12999,7 @@
         <v>839</v>
       </c>
       <c r="E160" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -13052,7 +13055,7 @@
         <v>840</v>
       </c>
       <c r="E161" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F161">
         <v>4.6</v>
@@ -13108,7 +13111,7 @@
         <v>841</v>
       </c>
       <c r="E162" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F162">
         <v>85</v>
@@ -13164,7 +13167,7 @@
         <v>842</v>
       </c>
       <c r="E163" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F163">
         <v>8.9</v>
@@ -13220,7 +13223,7 @@
         <v>843</v>
       </c>
       <c r="E164" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F164">
         <v>32.7</v>
@@ -13276,7 +13279,7 @@
         <v>844</v>
       </c>
       <c r="E165" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F165">
         <v>5.8</v>
@@ -13332,7 +13335,7 @@
         <v>845</v>
       </c>
       <c r="E166" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F166">
         <v>17.5</v>
@@ -13388,7 +13391,7 @@
         <v>846</v>
       </c>
       <c r="E167" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F167">
         <v>253.3</v>
@@ -13444,7 +13447,7 @@
         <v>847</v>
       </c>
       <c r="E168" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F168">
         <v>41.9</v>
@@ -13500,7 +13503,7 @@
         <v>848</v>
       </c>
       <c r="E169" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="F169">
         <v>453.6</v>
@@ -13556,7 +13559,7 @@
         <v>849</v>
       </c>
       <c r="E170" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F170">
         <v>40.5</v>
@@ -13612,7 +13615,7 @@
         <v>850</v>
       </c>
       <c r="E171" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F171">
         <v>9.699999999999999</v>
@@ -13668,7 +13671,7 @@
         <v>851</v>
       </c>
       <c r="E172" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="F172">
         <v>24.4</v>
@@ -13724,7 +13727,7 @@
         <v>852</v>
       </c>
       <c r="E173" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="F173">
         <v>21.8</v>
@@ -13780,7 +13783,7 @@
         <v>853</v>
       </c>
       <c r="E174" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F174">
         <v>71.7</v>
@@ -13836,7 +13839,7 @@
         <v>854</v>
       </c>
       <c r="E175" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -13892,7 +13895,7 @@
         <v>855</v>
       </c>
       <c r="E176" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F176">
         <v>1136.8</v>
@@ -13948,7 +13951,7 @@
         <v>856</v>
       </c>
       <c r="E177" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F177">
         <v>641.5</v>
@@ -14004,7 +14007,7 @@
         <v>857</v>
       </c>
       <c r="E178" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F178">
         <v>191.9</v>
@@ -14060,7 +14063,7 @@
         <v>858</v>
       </c>
       <c r="E179" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F179">
         <v>53.8</v>
@@ -14116,7 +14119,7 @@
         <v>859</v>
       </c>
       <c r="E180" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F180">
         <v>49.6</v>
@@ -14172,7 +14175,7 @@
         <v>860</v>
       </c>
       <c r="E181" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F181">
         <v>14.3</v>
@@ -14228,7 +14231,7 @@
         <v>861</v>
       </c>
       <c r="E182" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F182">
         <v>5.5</v>
@@ -14284,7 +14287,7 @@
         <v>862</v>
       </c>
       <c r="E183" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F183">
         <v>33.2</v>
@@ -14340,7 +14343,7 @@
         <v>863</v>
       </c>
       <c r="E184" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F184">
         <v>4.9</v>
@@ -14396,7 +14399,7 @@
         <v>864</v>
       </c>
       <c r="E185" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F185">
         <v>18</v>
@@ -14452,7 +14455,7 @@
         <v>865</v>
       </c>
       <c r="E186" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F186">
         <v>20.9</v>
@@ -14508,7 +14511,7 @@
         <v>866</v>
       </c>
       <c r="E187" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F187">
         <v>13.3</v>
@@ -14564,7 +14567,7 @@
         <v>867</v>
       </c>
       <c r="E188" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="F188">
         <v>14.1</v>
@@ -14620,7 +14623,7 @@
         <v>868</v>
       </c>
       <c r="E189" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F189">
         <v>5.5</v>
@@ -14676,7 +14679,7 @@
         <v>869</v>
       </c>
       <c r="E190" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F190">
         <v>11.9</v>
@@ -14732,7 +14735,7 @@
         <v>870</v>
       </c>
       <c r="E191" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F191">
         <v>13.3</v>
@@ -14788,7 +14791,7 @@
         <v>871</v>
       </c>
       <c r="E192" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="F192">
         <v>13.7</v>
@@ -14844,7 +14847,7 @@
         <v>872</v>
       </c>
       <c r="E193" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F193">
         <v>10.4</v>
@@ -14900,7 +14903,7 @@
         <v>873</v>
       </c>
       <c r="E194" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F194">
         <v>6.1</v>
@@ -14956,7 +14959,7 @@
         <v>874</v>
       </c>
       <c r="E195" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F195">
         <v>15.1</v>
@@ -15012,7 +15015,7 @@
         <v>875</v>
       </c>
       <c r="E196" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="F196">
         <v>346.8</v>
@@ -15068,7 +15071,7 @@
         <v>876</v>
       </c>
       <c r="E197" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F197">
         <v>173.6</v>
@@ -15124,7 +15127,7 @@
         <v>877</v>
       </c>
       <c r="E198" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="F198">
         <v>0</v>
@@ -15180,7 +15183,7 @@
         <v>878</v>
       </c>
       <c r="E199" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F199">
         <v>22.8</v>
@@ -15236,7 +15239,7 @@
         <v>879</v>
       </c>
       <c r="E200" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F200">
         <v>9.6</v>
@@ -15292,7 +15295,7 @@
         <v>880</v>
       </c>
       <c r="E201" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="F201">
         <v>5.9</v>
@@ -15348,7 +15351,7 @@
         <v>881</v>
       </c>
       <c r="E202" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F202">
         <v>24.7</v>
@@ -15404,7 +15407,7 @@
         <v>882</v>
       </c>
       <c r="E203" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="F203">
         <v>12.9</v>
@@ -15460,7 +15463,7 @@
         <v>883</v>
       </c>
       <c r="E204" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -15516,7 +15519,7 @@
         <v>884</v>
       </c>
       <c r="E205" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="F205">
         <v>24.3</v>
@@ -15572,7 +15575,7 @@
         <v>885</v>
       </c>
       <c r="E206" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="F206">
         <v>29.6</v>
@@ -15628,7 +15631,7 @@
         <v>886</v>
       </c>
       <c r="E207" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F207">
         <v>36.2</v>
@@ -15684,7 +15687,7 @@
         <v>887</v>
       </c>
       <c r="E208" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="F208">
         <v>3.5</v>
@@ -15740,7 +15743,7 @@
         <v>888</v>
       </c>
       <c r="E209" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="F209">
         <v>3.8</v>
@@ -15796,7 +15799,7 @@
         <v>889</v>
       </c>
       <c r="E210" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F210">
         <v>2681</v>
@@ -15852,7 +15855,7 @@
         <v>890</v>
       </c>
       <c r="E211" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F211">
         <v>239</v>
@@ -15908,7 +15911,7 @@
         <v>891</v>
       </c>
       <c r="E212" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F212">
         <v>257</v>
@@ -15964,7 +15967,7 @@
         <v>892</v>
       </c>
       <c r="E213" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="F213">
         <v>193.9</v>
@@ -16020,7 +16023,7 @@
         <v>893</v>
       </c>
       <c r="E214" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="F214">
         <v>195.7</v>
@@ -16076,7 +16079,7 @@
         <v>894</v>
       </c>
       <c r="E215" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F215">
         <v>160.3</v>
@@ -16132,7 +16135,7 @@
         <v>895</v>
       </c>
       <c r="E216" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F216">
         <v>207.8</v>
@@ -16188,7 +16191,7 @@
         <v>896</v>
       </c>
       <c r="E217" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="F217">
         <v>303.1</v>
@@ -16244,7 +16247,7 @@
         <v>897</v>
       </c>
       <c r="E218" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F218">
         <v>281.1</v>
@@ -16300,7 +16303,7 @@
         <v>898</v>
       </c>
       <c r="E219" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F219">
         <v>180.2</v>
@@ -16356,7 +16359,7 @@
         <v>899</v>
       </c>
       <c r="E220" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="F220">
         <v>338.5</v>
@@ -16412,7 +16415,7 @@
         <v>900</v>
       </c>
       <c r="E221" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F221">
         <v>0</v>
@@ -16468,7 +16471,7 @@
         <v>901</v>
       </c>
       <c r="E222" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="F222">
         <v>324.3</v>
@@ -16522,184 +16525,184 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B2" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="C2" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="D2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E2" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="F2" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="G2" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="H2" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B3" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="C3" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="D3" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="E3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="F3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="G3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B4" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C4" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D4" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="E4" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="F4" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="G4" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="H4" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B5" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="C5" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="D5" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="E5" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="F5" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="G5" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="H5" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C6" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D6" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="E6" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="F6" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="G6" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="H6" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B7" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C7" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D7" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E7" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="F7" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="G7" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="H7" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -16707,233 +16710,233 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C8" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="D8" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="E8" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="F8" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="G8" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H8" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B9" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C9" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D9" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B10" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C10" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D10" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="E10" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="F10" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="G10" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="H10" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B11" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="C11" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="D11" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="E11" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="F11" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="G11" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H11" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B12" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C12" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D12" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E12" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F12" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="G12" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H12" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B13" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C13" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D13" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E13" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F13" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="G13" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H13" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B14" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C14" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="D14" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="E14" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="F14" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="G14" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="H14" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B15" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="C15" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D15" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="E15" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="G15" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H15" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B16" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C16" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D16" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="E16" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="F16" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="G16" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H16" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
   </sheetData>
